--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Setting up Airflow/airflow_setup_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Setting up Airflow/airflow_setup_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airflow Setup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,15 +454,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pip install apache-airflow</t>
+          <t>Installation via pip is the first step.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Installation via pip is the first step.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -477,15 +476,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>airflow db init</t>
+          <t>This command creates the database tables.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>This command creates the database tables.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -500,15 +498,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AIRFLOW_HOME</t>
+          <t>AIRFLOW_HOME sets the location for Airflow files.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AIRFLOW_HOME sets the location for Airflow files.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -523,15 +520,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>~/airflow/airflow.cfg</t>
+          <t>The configuration file defaults to AIRFLOW_HOME.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The configuration file defaults to AIRFLOW_HOME.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -546,15 +542,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>airflow users create</t>
+          <t>Use this command to create a user for the UI.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Use this command to create a user for the UI.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -569,15 +564,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>airflow webserver</t>
+          <t>This starts the web interface.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>This starts the web interface.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -592,15 +586,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>airflow scheduler</t>
+          <t>This starts the scheduler process.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>This starts the scheduler process.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -622,12 +615,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SQLite is only for development/ testing.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SQLite is only for development/ testing.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -642,15 +635,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>Python 3.8 is commonly used and well-supported.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Python 3.8 is commonly used and well-supported.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -665,15 +657,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Configure executor in airflow.cfg</t>
+          <t>Set executor = CeleryExecutor in airflow.cfg.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Set executor = CeleryExecutor in airflow.cfg.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -695,12 +686,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>The Python scripts directory needs to be in PATH.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The Python scripts directory needs to be in PATH.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -715,15 +706,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>It stores all Airflow configuration settings.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>It stores all Airflow configuration settings.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -745,12 +735,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Redis and RabbitMQ are the officially supported brokers.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redis and RabbitMQ are the officially supported brokers.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -765,15 +755,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>airflow config get-value</t>
+          <t>This shows current configuration values.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>This shows current configuration values.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -788,15 +777,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>300 seconds</t>
+          <t>The scheduler checks for DAG changes every 5 minutes.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The scheduler checks for DAG changes every 5 minutes.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -811,15 +799,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AIRFLOW__{SECTION}__{KEY}</t>
+          <t>Use environment variables with double underscores.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Use environment variables with double underscores.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -834,15 +821,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>airflow dags list</t>
+          <t>This shows all DAGs in the dags folder.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>This shows all DAGs in the dags folder.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -864,12 +850,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>The required Python module needs to be installed.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The required Python module needs to be installed.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -884,15 +870,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>airflow dags pause</t>
+          <t>Use this to pause DAG scheduling.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Use this to pause DAG scheduling.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -907,15 +892,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>plugins folder</t>
+          <t>Use the plugins folder for custom operators and hooks.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Use the plugins folder for custom operators and hooks.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
